--- a/public/plantilla-ficha-hidrocarburos.xlsx
+++ b/public/plantilla-ficha-hidrocarburos.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="170" formatCode="&quot;$ &quot;#,##0.00"/>
     <numFmt numFmtId="171" formatCode="&quot;$ &quot;#,##0"/>
   </numFmts>
-  <fonts count="170">
+  <fonts count="173">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1242,6 +1242,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -6489,7 +6503,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1386">
+  <cellXfs count="1393">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9899,6 +9913,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="397" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="51" fillId="3" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="170" fillId="77" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="170" fillId="76" borderId="393" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="76" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="170" fillId="76" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="77" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="170" fillId="77" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="392" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -10261,6 +10296,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="50.77734375" customWidth="1" style="630" min="1" max="2"/>
+    <col width="13" customWidth="1" style="614" min="2" max="2"/>
     <col width="15.77734375" customWidth="1" style="630" min="3" max="4"/>
     <col width="13" customWidth="1" style="630" min="5" max="5"/>
     <col width="8.88671875" customWidth="1" style="630" min="6" max="16384"/>
@@ -10434,13 +10470,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="16" customHeight="1" s="614">
       <c r="A14" s="606" t="inlineStr">
         <is>
           <t>Componente de Obra Civil (Sí/No)</t>
         </is>
       </c>
-      <c r="B14" s="612" t="inlineStr">
+      <c r="B14" s="1386" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -10449,13 +10485,13 @@
       <c r="D14" s="611" t="n"/>
       <c r="E14" s="611" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="55" customHeight="1" s="614">
       <c r="A15" s="608" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Adecuación de terrenos (Pad/Cluster)</t>
         </is>
       </c>
-      <c r="B15" s="584" t="inlineStr">
+      <c r="B15" s="1387" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Adecuación de terrenos (Pad/Cluster)  —  Sí</t>
         </is>
@@ -10464,13 +10500,13 @@
       <c r="D15" s="607" t="n"/>
       <c r="E15" s="607" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="42" customHeight="1" s="614">
       <c r="A16" s="606" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Vías de acceso industrial</t>
         </is>
       </c>
-      <c r="B16" s="605" t="inlineStr">
+      <c r="B16" s="1386" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Vías de acceso industrial  —  Sí</t>
         </is>
@@ -10479,13 +10515,13 @@
       <c r="D16" s="604" t="n"/>
       <c r="E16" s="604" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="68" customHeight="1" s="614">
       <c r="A17" s="608" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Cimentaciones especiales (pilotes, zapatas, losas)</t>
         </is>
       </c>
-      <c r="B17" s="584" t="inlineStr">
+      <c r="B17" s="1387" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Cimentaciones especiales (pilotes, zapatas, losas)  —  Sí</t>
         </is>
@@ -10494,13 +10530,13 @@
       <c r="D17" s="607" t="n"/>
       <c r="E17" s="607" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="68" customHeight="1" s="614">
       <c r="A18" s="606" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Sistemas de contención secundaria (diques)</t>
         </is>
       </c>
-      <c r="B18" s="605" t="inlineStr">
+      <c r="B18" s="1386" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Sistemas de contención secundaria (diques)  —  Sí</t>
         </is>
@@ -10509,13 +10545,13 @@
       <c r="D18" s="604" t="n"/>
       <c r="E18" s="604" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="55" customHeight="1" s="614">
       <c r="A19" s="608" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Manejo de aguas - drenaje aceitoso</t>
         </is>
       </c>
-      <c r="B19" s="584" t="inlineStr">
+      <c r="B19" s="1387" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Manejo de aguas - drenaje aceitoso  —  Sí</t>
         </is>
@@ -10524,13 +10560,13 @@
       <c r="D19" s="607" t="n"/>
       <c r="E19" s="607" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="55" customHeight="1" s="614">
       <c r="A20" s="606" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Manejo de aguas - drenaje pluvial</t>
         </is>
       </c>
-      <c r="B20" s="605" t="inlineStr">
+      <c r="B20" s="1386" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Manejo de aguas - drenaje pluvial  —  Sí</t>
         </is>
@@ -10539,13 +10575,13 @@
       <c r="D20" s="604" t="n"/>
       <c r="E20" s="604" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="16" customHeight="1" s="614">
       <c r="A21" s="608" t="inlineStr">
         <is>
           <t>Componente de Construcción y Facilidades Mecánicas (Sí/No)</t>
         </is>
       </c>
-      <c r="B21" s="610" t="inlineStr">
+      <c r="B21" s="1387" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -10554,13 +10590,13 @@
       <c r="D21" s="609" t="n"/>
       <c r="E21" s="609" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="55" customHeight="1" s="614">
       <c r="A22" s="606" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Sistemas de separación (bifásicos/trifásicos)</t>
         </is>
       </c>
-      <c r="B22" s="605" t="inlineStr">
+      <c r="B22" s="1386" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Sistemas de separación (bifásicos/trifásicos)</t>
         </is>
@@ -10569,13 +10605,13 @@
       <c r="D22" s="604" t="n"/>
       <c r="E22" s="604" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="55" customHeight="1" s="614">
       <c r="A23" s="608" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Almacenamiento de fluidos - tanques API 650</t>
         </is>
       </c>
-      <c r="B23" s="584" t="inlineStr">
+      <c r="B23" s="1387" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Almacenamiento de fluidos - tanques API 650</t>
         </is>
@@ -10584,13 +10620,13 @@
       <c r="D23" s="607" t="n"/>
       <c r="E23" s="607" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="42" customHeight="1" s="614">
       <c r="A24" s="606" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Sistemas de bombeo y transferencia</t>
         </is>
       </c>
-      <c r="B24" s="605" t="inlineStr">
+      <c r="B24" s="1386" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Sistemas de bombeo y transferencia</t>
         </is>
@@ -10599,13 +10635,13 @@
       <c r="D24" s="604" t="n"/>
       <c r="E24" s="604" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="55" customHeight="1" s="614">
       <c r="A25" s="608" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Líneas de flujo y colectores (Manifolds)</t>
         </is>
       </c>
-      <c r="B25" s="584" t="inlineStr">
+      <c r="B25" s="1387" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Líneas de flujo y colectores (Manifolds)  —  Sí</t>
         </is>
@@ -10614,13 +10650,13 @@
       <c r="D25" s="607" t="n"/>
       <c r="E25" s="607" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="55" customHeight="1" s="614">
       <c r="A26" s="606" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Tratamiento de gas (Scrubbers, Tea/Flare)</t>
         </is>
       </c>
-      <c r="B26" s="605" t="inlineStr">
+      <c r="B26" s="1386" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Tratamiento de gas (Scrubbers, Tea/Flare)</t>
         </is>
@@ -10629,13 +10665,13 @@
       <c r="D26" s="604" t="n"/>
       <c r="E26" s="604" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="16" customHeight="1" s="614">
       <c r="A27" s="608" t="inlineStr">
         <is>
           <t>Componente Eléctrico, Instrumentación y Control (Sí/No)</t>
         </is>
       </c>
-      <c r="B27" s="610" t="inlineStr">
+      <c r="B27" s="1387" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -10644,13 +10680,13 @@
       <c r="D27" s="609" t="n"/>
       <c r="E27" s="609" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="68" customHeight="1" s="614">
       <c r="A28" s="606" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Generación y distribución (subestaciones, redes)</t>
         </is>
       </c>
-      <c r="B28" s="605" t="inlineStr">
+      <c r="B28" s="1386" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Generación y distribución (subestaciones, redes)  —  Sí</t>
         </is>
@@ -10659,13 +10695,13 @@
       <c r="D28" s="604" t="n"/>
       <c r="E28" s="604" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="55" customHeight="1" s="614">
       <c r="A29" s="608" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Automatización (DCS / SCADA)</t>
         </is>
       </c>
-      <c r="B29" s="584" t="inlineStr">
+      <c r="B29" s="1387" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Automatización (DCS / SCADA)  —  Sí</t>
         </is>
@@ -10674,13 +10710,13 @@
       <c r="D29" s="607" t="n"/>
       <c r="E29" s="607" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="55" customHeight="1" s="614">
       <c r="A30" s="606" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Seguridad activa (SIS, SDV/BDV, F&amp;G)</t>
         </is>
       </c>
-      <c r="B30" s="605" t="inlineStr">
+      <c r="B30" s="1386" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Seguridad activa (SIS, SDV/BDV, F&amp;G)  —  Sí</t>
         </is>
@@ -10703,52 +10739,52 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="576" t="inlineStr">
+    <row r="33" ht="16" customHeight="1" s="614">
+      <c r="A33" s="1388" t="inlineStr">
         <is>
           <t>Administración (A)</t>
         </is>
       </c>
-      <c r="B33" s="1381" t="n">
+      <c r="B33" s="1389" t="n">
         <v>0.1</v>
       </c>
       <c r="C33" s="574" t="n"/>
       <c r="D33" s="574" t="n"/>
       <c r="E33" s="574" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="580" t="inlineStr">
+    <row r="34" ht="16" customHeight="1" s="614">
+      <c r="A34" s="1390" t="inlineStr">
         <is>
           <t>Imprevistos (I)</t>
         </is>
       </c>
-      <c r="B34" s="1382" t="n">
+      <c r="B34" s="1391" t="n">
         <v>0.04</v>
       </c>
       <c r="C34" s="577" t="n"/>
       <c r="D34" s="577" t="n"/>
       <c r="E34" s="577" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="576" t="inlineStr">
+    <row r="35" ht="16" customHeight="1" s="614">
+      <c r="A35" s="1388" t="inlineStr">
         <is>
           <t>Utilidad (U)</t>
         </is>
       </c>
-      <c r="B35" s="1381" t="n">
+      <c r="B35" s="1389" t="n">
         <v>0.12</v>
       </c>
       <c r="C35" s="574" t="n"/>
       <c r="D35" s="574" t="n"/>
       <c r="E35" s="574" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="580" t="inlineStr">
+    <row r="36" ht="16" customHeight="1" s="614">
+      <c r="A36" s="1390" t="inlineStr">
         <is>
           <t>IVA sobre Utilidad</t>
         </is>
       </c>
-      <c r="B36" s="1382" t="n">
+      <c r="B36" s="1391" t="n">
         <v>0.19</v>
       </c>
       <c r="C36" s="577" t="n"/>
@@ -10762,8 +10798,8 @@
       <c r="D37" s="1383" t="n"/>
       <c r="E37" s="1384" t="n"/>
     </row>
-    <row r="38">
-      <c r="A38" s="573" t="inlineStr">
+    <row r="38" ht="16" customHeight="1" s="614">
+      <c r="A38" s="1392" t="inlineStr">
         <is>
           <t>AIU TOTAL (A+I+U)</t>
         </is>
